--- a/zy70670/test_invalid_references.xlsx
+++ b/zy70670/test_invalid_references.xlsx
@@ -497,15 +497,15 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>常见问题解答</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>3</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>产品B配置说明</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -515,12 +515,12 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>/docs/product-a-api.md</t>
+          <t>/docs/product-b-config.md</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>产品A的API</t>
+          <t>产品B配置说明</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -538,17 +538,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>关联产品已下线: 产品B</t>
+          <t>引用了已下线产品: 产品B (状态: end_of_life)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-05-18 06:42:15</t>
+          <t>2026-05-19 05:51:10</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-05-17 22:42:15</t>
+          <t>2026-05-18 21:51:10</t>
         </is>
       </c>
     </row>

--- a/zy70670/test_invalid_references.xlsx
+++ b/zy70670/test_invalid_references.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,22 +497,24 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>常见问题解答</t>
+          <t>产品A使用指南</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>产品B配置说明</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>/docs/product-b-config.md</t>
@@ -543,12 +545,67 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-05-19 05:51:10</t>
+          <t>2026-05-19 06:06:24</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-05-18 21:51:10</t>
+          <t>2026-05-18 22:06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>常见问题解答</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>产品B配置说明</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>/docs/product-b-config.md</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>产品B配置说明</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>needs_manual_review</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>product_offline</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>引用了已下线产品: 产品B (状态: end_of_life)</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:06:24</t>
         </is>
       </c>
     </row>
